--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,20 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A49FF4-59ED-4FFE-BF8A-A26F3EDDABC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241C0460-3E73-48BC-910D-4614BEBB773B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
   <sheets>
     <sheet name="WC_2026" sheetId="1" r:id="rId1"/>
     <sheet name="Historic_Data" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -1240,11 +1251,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -1292,9 +1303,75 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46185</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2">
+        <v>1881</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2">
+        <v>1511</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
       <c r="K2">
         <f>IF(E2&gt;H2, 2, IF(E2=H2, 1, 0))</f>
-        <v>1</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46185</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3">
+        <v>1758</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3">
+        <v>1740</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <f>IF(E3&gt;H3, 2, IF(E3=H3, 1, 0))</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241C0460-3E73-48BC-910D-4614BEBB773B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2979D1-7744-48A3-AEC2-A22523A6F6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -1251,15 +1251,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -1371,6 +1371,78 @@
       </c>
       <c r="K3">
         <f>IF(E3&gt;H3, 2, IF(E3=H3, 1, 0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46186</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4">
+        <v>1767</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4">
+        <v>1616</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ref="K4:K5" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46186</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>1726</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5">
+        <v>1834</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2979D1-7744-48A3-AEC2-A22523A6F6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DB5504-1225-4C94-8FA4-698844F30B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -1251,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K5" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K9" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1442,6 +1442,150 @@
         <v>0</v>
       </c>
       <c r="K5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46187</v>
+      </c>
+      <c r="C6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6">
+        <v>1447</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6">
+        <v>1865</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46187</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7">
+        <v>1978</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7">
+        <v>1840</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46187</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8">
+        <v>1548</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8">
+        <v>1782</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46187</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>1777</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9">
+        <v>1911</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DB5504-1225-4C94-8FA4-698844F30B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67286DCB-8C07-4460-8CDD-C25F26D50656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -1251,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K9" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K13" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1586,6 +1586,150 @@
         <v>1</v>
       </c>
       <c r="K9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10">
+        <v>1939</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10">
+        <v>1427</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11">
+        <v>1944</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11">
+        <v>1910</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12">
+        <v>1695</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12">
+        <v>1938</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13">
+        <v>1712</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13">
+        <v>1628</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67286DCB-8C07-4460-8CDD-C25F26D50656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF96CB5-89B2-43AE-A531-3D2D4F275ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -1251,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K13" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K17" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1732,6 +1732,150 @@
       <c r="K13">
         <f t="shared" si="0"/>
         <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46189</v>
+      </c>
+      <c r="C14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14">
+        <v>2129</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14">
+        <v>1606</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46189</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>1879</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15">
+        <v>1711</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46189</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16">
+        <v>1598</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>1870</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46189</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17">
+        <v>1772</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17">
+        <v>1562</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF96CB5-89B2-43AE-A531-3D2D4F275ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D968C9-14C4-41E4-A921-68C0233AE58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -1251,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K17" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K21" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1876,6 +1876,150 @@
       <c r="K17">
         <f t="shared" si="0"/>
         <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46190</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18">
+        <v>2084</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18">
+        <v>1839</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46190</v>
+      </c>
+      <c r="C19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19">
+        <v>1592</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19">
+        <v>1929</v>
+      </c>
+      <c r="H19">
+        <v>4</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46190</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20">
+        <v>2128</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20">
+        <v>1759</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46190</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21">
+        <v>1857</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21">
+        <v>1653</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D968C9-14C4-41E4-A921-68C0233AE58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D43740-CFD9-47C7-A885-CFC7B01014A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -1251,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K21" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K25" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -2020,6 +2020,150 @@
       <c r="K21">
         <f t="shared" si="0"/>
         <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46191</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22">
+        <v>1967</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1674</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46191</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23">
+        <v>2055</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23">
+        <v>1881</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46191</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24">
+        <v>1510</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24">
+        <v>1730</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46191</v>
+      </c>
+      <c r="C25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25">
+        <v>1714</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25">
+        <v>1982</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D43740-CFD9-47C7-A885-CFC7B01014A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5882D7-AA56-4490-85E7-9C10480DBFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -1251,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K25" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K29" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -2164,6 +2164,150 @@
       <c r="K25">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46192</v>
+      </c>
+      <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26">
+        <v>1696</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>107</v>
+      </c>
+      <c r="G26">
+        <v>1527</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46192</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27">
+        <v>1885</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27">
+        <v>1596</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46192</v>
+      </c>
+      <c r="C28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28">
+        <v>1777</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28">
+        <v>1437</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46192</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29">
+        <v>1896</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29">
+        <v>1771</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5882D7-AA56-4490-85E7-9C10480DBFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7176DAAE-9B1E-4BA7-A471-93CD5BFB2DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -1251,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K29" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K33" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -2308,6 +2308,150 @@
       <c r="K29">
         <f t="shared" si="0"/>
         <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46193</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30">
+        <v>1820</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30">
+        <v>1799</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46193</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31">
+        <v>1768</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31">
+        <v>1866</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46193</v>
+      </c>
+      <c r="C32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32">
+        <v>1986</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32">
+        <v>1528</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46193</v>
+      </c>
+      <c r="C33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33">
+        <v>1813</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33">
+        <v>1816</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7176DAAE-9B1E-4BA7-A471-93CD5BFB2DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E61C3F9-5755-46A5-959F-7A4E8A190F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -410,6 +410,9 @@
   </si>
   <si>
     <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>Ivory  Coast</t>
   </si>
 </sst>
 </file>
@@ -1251,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1406,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K33" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K37" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -2450,6 +2453,150 @@
         <v>1</v>
       </c>
       <c r="K33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34">
+        <v>1972</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="F34" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34">
+        <v>1727</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35">
+        <v>1954</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>126</v>
+      </c>
+      <c r="G35">
+        <v>1728</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C36" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36">
+        <v>1890</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36">
+        <v>1427</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C37" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37">
+        <v>1585</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="s">
+        <v>43</v>
+      </c>
+      <c r="G37">
+        <v>1910</v>
+      </c>
+      <c r="H37">
+        <v>4</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E61C3F9-5755-46A5-959F-7A4E8A190F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969F0901-B19B-4A03-B33A-42BE66778A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K37" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K41" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -2597,6 +2597,150 @@
         <v>1</v>
       </c>
       <c r="K37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C38" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38">
+        <v>2134</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38">
+        <v>1593</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39">
+        <v>1869</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" t="s">
+        <v>54</v>
+      </c>
+      <c r="G39">
+        <v>1766</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40">
+        <v>1851</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40">
+        <v>1625</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41">
+        <v>1549</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41">
+        <v>1740</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969F0901-B19B-4A03-B33A-42BE66778A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14E229E-E372-4CB2-B4D5-54B1272DDD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K41" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K45" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -2741,6 +2741,150 @@
         <v>1</v>
       </c>
       <c r="K41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42">
+        <v>2144</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42" t="s">
+        <v>28</v>
+      </c>
+      <c r="G42">
+        <v>1841</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C43" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43">
+        <v>2084</v>
+      </c>
+      <c r="E43">
+        <v>3</v>
+      </c>
+      <c r="F43" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43">
+        <v>1592</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C44" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44">
+        <v>1929</v>
+      </c>
+      <c r="E44">
+        <v>3</v>
+      </c>
+      <c r="F44" t="s">
+        <v>46</v>
+      </c>
+      <c r="G44">
+        <v>1839</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C45" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45">
+        <v>1653</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45">
+        <v>1759</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14E229E-E372-4CB2-B4D5-54B1272DDD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16BFC47-A0A6-4C20-9D5A-A6C1033D7A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K45" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K49" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -2887,6 +2887,150 @@
       <c r="K45">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46">
+        <v>1988</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46" t="s">
+        <v>90</v>
+      </c>
+      <c r="G46">
+        <v>1677</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C47" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47">
+        <v>2028</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47">
+        <v>1584</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48">
+        <v>1668</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="s">
+        <v>44</v>
+      </c>
+      <c r="G48">
+        <v>1896</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49">
+        <v>1998</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49">
+        <v>1674</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16BFC47-A0A6-4C20-9D5A-A6C1033D7A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C758F36-B82B-482D-BB19-A8F7FECF5CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,12 +1254,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K49" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K55" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -3029,6 +3029,222 @@
         <v>1</v>
       </c>
       <c r="K49">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C50" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50">
+        <v>1622</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+      <c r="F50" t="s">
+        <v>112</v>
+      </c>
+      <c r="G50">
+        <v>1411</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C51" t="s">
+        <v>81</v>
+      </c>
+      <c r="D51">
+        <v>1914</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51" t="s">
+        <v>47</v>
+      </c>
+      <c r="G51">
+        <v>1748</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52">
+        <v>1877</v>
+      </c>
+      <c r="E52">
+        <v>4</v>
+      </c>
+      <c r="F52" t="s">
+        <v>85</v>
+      </c>
+      <c r="G52">
+        <v>1517</v>
+      </c>
+      <c r="H52">
+        <v>2</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C53" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53">
+        <v>1745</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53" t="s">
+        <v>41</v>
+      </c>
+      <c r="G53">
+        <v>2009</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C54" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54">
+        <v>1680</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
+        <v>37</v>
+      </c>
+      <c r="G54">
+        <v>1912</v>
+      </c>
+      <c r="H54">
+        <v>3</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C55" t="s">
+        <v>107</v>
+      </c>
+      <c r="D55">
+        <v>1575</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>31</v>
+      </c>
+      <c r="G55">
+        <v>1723</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C758F36-B82B-482D-BB19-A8F7FECF5CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A569CC36-7435-4412-950F-BFB0ED6DAD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K55" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K61" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -3245,6 +3245,222 @@
         <v>1</v>
       </c>
       <c r="K55">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C56" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56">
+        <v>1438</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56" t="s">
+        <v>126</v>
+      </c>
+      <c r="G56">
+        <v>1743</v>
+      </c>
+      <c r="H56">
+        <v>2</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57">
+        <v>1902</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57" t="s">
+        <v>80</v>
+      </c>
+      <c r="G57">
+        <v>1916</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58">
+        <v>1910</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>121</v>
+      </c>
+      <c r="G58">
+        <v>1742</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C59" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59">
+        <v>1562</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>69</v>
+      </c>
+      <c r="G59">
+        <v>1980</v>
+      </c>
+      <c r="H59">
+        <v>3</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C60" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60">
+        <v>1816</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60">
+        <v>1799</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C61" t="s">
+        <v>120</v>
+      </c>
+      <c r="D61">
+        <v>1813</v>
+      </c>
+      <c r="E61">
+        <v>3</v>
+      </c>
+      <c r="F61" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61">
+        <v>1820</v>
+      </c>
+      <c r="H61">
+        <v>2</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A569CC36-7435-4412-950F-BFB0ED6DAD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C755A522-402F-44D4-B0F7-C7FCC1F55FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K61" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K67" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -3463,6 +3463,222 @@
       <c r="K61">
         <f t="shared" si="0"/>
         <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C62" t="s">
+        <v>104</v>
+      </c>
+      <c r="D62">
+        <v>1918</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62">
+        <v>2123</v>
+      </c>
+      <c r="H62">
+        <v>4</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C63" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63">
+        <v>1842</v>
+      </c>
+      <c r="E63">
+        <v>5</v>
+      </c>
+      <c r="F63" t="s">
+        <v>91</v>
+      </c>
+      <c r="G63">
+        <v>1561</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C64" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64">
+        <v>1622</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64" t="s">
+        <v>72</v>
+      </c>
+      <c r="G64">
+        <v>1596</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65">
+        <v>1841</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65" t="s">
+        <v>71</v>
+      </c>
+      <c r="G65">
+        <v>2144</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C66" t="s">
+        <v>53</v>
+      </c>
+      <c r="D66">
+        <v>1740</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>54</v>
+      </c>
+      <c r="G66">
+        <v>1766</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C67" t="s">
+        <v>56</v>
+      </c>
+      <c r="D67">
+        <v>1549</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>34</v>
+      </c>
+      <c r="G67">
+        <v>1869</v>
+      </c>
+      <c r="H67">
+        <v>5</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C755A522-402F-44D4-B0F7-C7FCC1F55FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC90862-B24D-4D87-8ACD-63632EC3A0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K67" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K73" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -3677,6 +3677,222 @@
         <v>1</v>
       </c>
       <c r="K67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46201</v>
+      </c>
+      <c r="C68" t="s">
+        <v>44</v>
+      </c>
+      <c r="D68">
+        <v>1905</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68" t="s">
+        <v>32</v>
+      </c>
+      <c r="G68">
+        <v>1575</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1">
+        <v>46201</v>
+      </c>
+      <c r="C69" t="s">
+        <v>108</v>
+      </c>
+      <c r="D69">
+        <v>1658</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69" t="s">
+        <v>74</v>
+      </c>
+      <c r="G69">
+        <v>2038</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1">
+        <v>46201</v>
+      </c>
+      <c r="C70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70">
+        <v>2004</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70" t="s">
+        <v>100</v>
+      </c>
+      <c r="G70">
+        <v>1990</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1">
+        <v>46201</v>
+      </c>
+      <c r="C71" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71">
+        <v>1712</v>
+      </c>
+      <c r="E71">
+        <v>3</v>
+      </c>
+      <c r="F71" t="s">
+        <v>90</v>
+      </c>
+      <c r="G71">
+        <v>1631</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1">
+        <v>46201</v>
+      </c>
+      <c r="C72" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72">
+        <v>1785</v>
+      </c>
+      <c r="E72">
+        <v>3</v>
+      </c>
+      <c r="F72" t="s">
+        <v>28</v>
+      </c>
+      <c r="G72">
+        <v>1836</v>
+      </c>
+      <c r="H72">
+        <v>3</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1">
+        <v>46201</v>
+      </c>
+      <c r="C73" t="s">
+        <v>92</v>
+      </c>
+      <c r="D73">
+        <v>1628</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73" t="s">
+        <v>17</v>
+      </c>
+      <c r="G73">
+        <v>2148</v>
+      </c>
+      <c r="H73">
+        <v>3</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC90862-B24D-4D87-8ACD-63632EC3A0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C1A252-4798-403C-8043-42FADB217A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K73" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K74" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -3893,6 +3893,42 @@
         <v>1</v>
       </c>
       <c r="K73">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1">
+        <v>46202</v>
+      </c>
+      <c r="C74" t="s">
+        <v>107</v>
+      </c>
+      <c r="D74">
+        <v>1559</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74" t="s">
+        <v>47</v>
+      </c>
+      <c r="G74">
+        <v>1764</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>2</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C1A252-4798-403C-8043-42FADB217A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A17AAB-E04E-48D1-A00B-8F62C033C39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K74" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K77" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -3931,6 +3931,114 @@
       <c r="K74">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46203</v>
+      </c>
+      <c r="C75" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75">
+        <v>2031</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75" t="s">
+        <v>43</v>
+      </c>
+      <c r="G75">
+        <v>1888</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>2</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1">
+        <v>46203</v>
+      </c>
+      <c r="C76" t="s">
+        <v>80</v>
+      </c>
+      <c r="D76">
+        <v>1908</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76" t="s">
+        <v>102</v>
+      </c>
+      <c r="G76">
+        <v>1823</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46203</v>
+      </c>
+      <c r="C77" t="s">
+        <v>69</v>
+      </c>
+      <c r="D77">
+        <v>1971</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77" t="s">
+        <v>70</v>
+      </c>
+      <c r="G77">
+        <v>1886</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77">
+        <v>2</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A17AAB-E04E-48D1-A00B-8F62C033C39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF0C94C-AE94-4AD9-8F40-8A74E8185B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K77" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K83" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -4039,6 +4039,222 @@
       <c r="K77">
         <f t="shared" si="0"/>
         <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46204</v>
+      </c>
+      <c r="C78" t="s">
+        <v>96</v>
+      </c>
+      <c r="D78">
+        <v>1727</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="F78" t="s">
+        <v>104</v>
+      </c>
+      <c r="G78">
+        <v>1934</v>
+      </c>
+      <c r="H78">
+        <v>2</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46204</v>
+      </c>
+      <c r="C79" t="s">
+        <v>42</v>
+      </c>
+      <c r="D79">
+        <v>2134</v>
+      </c>
+      <c r="E79">
+        <v>3</v>
+      </c>
+      <c r="F79" t="s">
+        <v>121</v>
+      </c>
+      <c r="G79">
+        <v>1731</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>2</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1">
+        <v>46204</v>
+      </c>
+      <c r="C80" t="s">
+        <v>37</v>
+      </c>
+      <c r="D80">
+        <v>1943</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="F80" t="s">
+        <v>49</v>
+      </c>
+      <c r="G80">
+        <v>1871</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>2</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46205</v>
+      </c>
+      <c r="C81" t="s">
+        <v>74</v>
+      </c>
+      <c r="D81">
+        <v>2046</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="F81" t="s">
+        <v>12</v>
+      </c>
+      <c r="G81">
+        <v>1704</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
+        <v>2</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46205</v>
+      </c>
+      <c r="C82" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82">
+        <v>1910</v>
+      </c>
+      <c r="E82">
+        <v>3</v>
+      </c>
+      <c r="F82" t="s">
+        <v>46</v>
+      </c>
+      <c r="G82">
+        <v>1816</v>
+      </c>
+      <c r="H82">
+        <v>2</v>
+      </c>
+      <c r="I82">
+        <v>2</v>
+      </c>
+      <c r="J82">
+        <v>1</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46205</v>
+      </c>
+      <c r="C83" t="s">
+        <v>25</v>
+      </c>
+      <c r="D83">
+        <v>1798</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="F83" t="s">
+        <v>33</v>
+      </c>
+      <c r="G83">
+        <v>1605</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF0C94C-AE94-4AD9-8F40-8A74E8185B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E693558D-DCD5-4410-8BBF-43C4BBB52F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K83" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K89" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -4253,6 +4253,222 @@
         <v>0</v>
       </c>
       <c r="K83">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46206</v>
+      </c>
+      <c r="C84" t="s">
+        <v>71</v>
+      </c>
+      <c r="D84">
+        <v>2159</v>
+      </c>
+      <c r="E84">
+        <v>3</v>
+      </c>
+      <c r="F84" t="s">
+        <v>28</v>
+      </c>
+      <c r="G84">
+        <v>1821</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46206</v>
+      </c>
+      <c r="C85" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85">
+        <v>2013</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="F85" t="s">
+        <v>44</v>
+      </c>
+      <c r="G85">
+        <v>1882</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85">
+        <v>2</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1">
+        <v>46206</v>
+      </c>
+      <c r="C86" t="s">
+        <v>81</v>
+      </c>
+      <c r="D86">
+        <v>1943</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="F86" t="s">
+        <v>8</v>
+      </c>
+      <c r="G86">
+        <v>1756</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1">
+        <v>46207</v>
+      </c>
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87">
+        <v>1795</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87" t="s">
+        <v>53</v>
+      </c>
+      <c r="G87">
+        <v>1747</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>2</v>
+      </c>
+      <c r="J87">
+        <v>1</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1">
+        <v>46207</v>
+      </c>
+      <c r="C88" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88">
+        <v>2151</v>
+      </c>
+      <c r="E88">
+        <v>3</v>
+      </c>
+      <c r="F88" t="s">
+        <v>50</v>
+      </c>
+      <c r="G88">
+        <v>1619</v>
+      </c>
+      <c r="H88">
+        <v>2</v>
+      </c>
+      <c r="I88">
+        <v>2</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1">
+        <v>46207</v>
+      </c>
+      <c r="C89" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89">
+        <v>2009</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89" t="s">
+        <v>32</v>
+      </c>
+      <c r="G89">
+        <v>1570</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>2</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="K89">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E693558D-DCD5-4410-8BBF-43C4BBB52F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921BC32F-81EE-46C4-A106-C7322261E8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K89" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K91" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -4471,6 +4471,78 @@
       <c r="K89">
         <f t="shared" si="0"/>
         <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1">
+        <v>46208</v>
+      </c>
+      <c r="C90" t="s">
+        <v>47</v>
+      </c>
+      <c r="D90">
+        <v>1729</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90" t="s">
+        <v>70</v>
+      </c>
+      <c r="G90">
+        <v>1921</v>
+      </c>
+      <c r="H90">
+        <v>3</v>
+      </c>
+      <c r="I90">
+        <v>3</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1">
+        <v>46208</v>
+      </c>
+      <c r="C91" t="s">
+        <v>102</v>
+      </c>
+      <c r="D91">
+        <v>1814</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91" t="s">
+        <v>42</v>
+      </c>
+      <c r="G91">
+        <v>2143</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
+        <v>3</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921BC32F-81EE-46C4-A106-C7322261E8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1236500D-0E71-4238-9673-39C05ADA47CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K91" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K93" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -4541,6 +4541,78 @@
         <v>1</v>
       </c>
       <c r="K91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1">
+        <v>46209</v>
+      </c>
+      <c r="C92" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92">
+        <v>1993</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92" t="s">
+        <v>104</v>
+      </c>
+      <c r="G92">
+        <v>1972</v>
+      </c>
+      <c r="H92">
+        <v>2</v>
+      </c>
+      <c r="I92">
+        <v>3</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1">
+        <v>46209</v>
+      </c>
+      <c r="C93" t="s">
+        <v>37</v>
+      </c>
+      <c r="D93">
+        <v>1913</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="F93" t="s">
+        <v>74</v>
+      </c>
+      <c r="G93">
+        <v>2076</v>
+      </c>
+      <c r="H93">
+        <v>3</v>
+      </c>
+      <c r="I93">
+        <v>3</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1236500D-0E71-4238-9673-39C05ADA47CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355845E4-7BDF-4817-B6B8-B659BF115526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K93" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K97" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -4615,6 +4615,150 @@
       <c r="K93">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1">
+        <v>46210</v>
+      </c>
+      <c r="C94" t="s">
+        <v>100</v>
+      </c>
+      <c r="D94">
+        <v>1995</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94" t="s">
+        <v>71</v>
+      </c>
+      <c r="G94">
+        <v>2177</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94">
+        <v>3</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1">
+        <v>46210</v>
+      </c>
+      <c r="C95" t="s">
+        <v>25</v>
+      </c>
+      <c r="D95">
+        <v>1747</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>34</v>
+      </c>
+      <c r="G95">
+        <v>1961</v>
+      </c>
+      <c r="H95">
+        <v>4</v>
+      </c>
+      <c r="I95">
+        <v>3</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1">
+        <v>46211</v>
+      </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96">
+        <v>2156</v>
+      </c>
+      <c r="E96">
+        <v>3</v>
+      </c>
+      <c r="F96" t="s">
+        <v>53</v>
+      </c>
+      <c r="G96">
+        <v>1742</v>
+      </c>
+      <c r="H96">
+        <v>2</v>
+      </c>
+      <c r="I96">
+        <v>3</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+      <c r="K96">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1">
+        <v>46211</v>
+      </c>
+      <c r="C97" t="s">
+        <v>81</v>
+      </c>
+      <c r="D97">
+        <v>1949</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97" t="s">
+        <v>24</v>
+      </c>
+      <c r="G97">
+        <v>2003</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>3</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355845E4-7BDF-4817-B6B8-B659BF115526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A47E1F8-472B-4E7A-8E70-E621E21AC09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K97" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K98" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -4759,6 +4759,42 @@
       <c r="K97">
         <f t="shared" si="0"/>
         <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1">
+        <v>46213</v>
+      </c>
+      <c r="C98" t="s">
+        <v>42</v>
+      </c>
+      <c r="D98">
+        <v>2163</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="F98" t="s">
+        <v>70</v>
+      </c>
+      <c r="G98">
+        <v>1901</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>4</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A47E1F8-472B-4E7A-8E70-E621E21AC09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17330D6E-CBD1-4A2D-B776-CA22F1474B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K98" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K99" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -4793,6 +4793,42 @@
         <v>1</v>
       </c>
       <c r="K98">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1">
+        <v>46214</v>
+      </c>
+      <c r="C99" t="s">
+        <v>71</v>
+      </c>
+      <c r="D99">
+        <v>2190</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99" t="s">
+        <v>34</v>
+      </c>
+      <c r="G99">
+        <v>1948</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>4</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17330D6E-CBD1-4A2D-B776-CA22F1474B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08318AE9-BA81-4250-9AD9-D4509140E9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K99" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K101" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -4829,6 +4829,78 @@
         <v>1</v>
       </c>
       <c r="K99">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1">
+        <v>46215</v>
+      </c>
+      <c r="C100" t="s">
+        <v>104</v>
+      </c>
+      <c r="D100">
+        <v>1951</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100" t="s">
+        <v>74</v>
+      </c>
+      <c r="G100">
+        <v>2097</v>
+      </c>
+      <c r="H100">
+        <v>2</v>
+      </c>
+      <c r="I100">
+        <v>4</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" s="1">
+        <v>46215</v>
+      </c>
+      <c r="C101" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101">
+        <v>2156</v>
+      </c>
+      <c r="E101">
+        <v>3</v>
+      </c>
+      <c r="F101" t="s">
+        <v>81</v>
+      </c>
+      <c r="G101">
+        <v>1949</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>4</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs\world_cup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08318AE9-BA81-4250-9AD9-D4509140E9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B27519A-A1BD-4768-8269-02D5B2F097C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5129E331-5CE9-4084-9F59-05652B25F4C8}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0676E7-9C9C-4876-9697-3A2602566485}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K101" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
+        <f t="shared" ref="K4:K103" si="0">IF(E4&gt;H4, 2, IF(E4=H4, 1, 0))</f>
         <v>1</v>
       </c>
     </row>
@@ -4903,6 +4903,78 @@
       <c r="K101">
         <f t="shared" si="0"/>
         <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C102" t="s">
+        <v>42</v>
+      </c>
+      <c r="D102">
+        <v>2121</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102" t="s">
+        <v>71</v>
+      </c>
+      <c r="G102">
+        <v>2232</v>
+      </c>
+      <c r="H102">
+        <v>2</v>
+      </c>
+      <c r="I102">
+        <v>5</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C103" t="s">
+        <v>74</v>
+      </c>
+      <c r="D103">
+        <v>2074</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+      <c r="F103" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103">
+        <v>2200</v>
+      </c>
+      <c r="H103">
+        <v>2</v>
+      </c>
+      <c r="I103">
+        <v>5</v>
+      </c>
+      <c r="J103">
+        <v>1</v>
+      </c>
+      <c r="K103">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
